--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_lastcheck.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_lastcheck.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,6 +146,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -158,7 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,12 +183,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,11 +807,11 @@
       <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>81.7</v>
+      <c r="G4" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -813,53 +819,53 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="S4" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T4" s="3" t="n">
+      <c r="R4" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+      <c r="X4" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z4" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -890,7 +896,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -898,53 +904,53 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+      <c r="M5" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q5" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>2</v>
+      <c r="S5" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>18.3</v>
+        <v>19.6</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>80.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -966,25 +972,25 @@
         <v>25.9</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G6" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>1.1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>11.1</v>
@@ -993,43 +999,43 @@
         <v>11</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>98.5</v>
+        <v>99.3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>11.9</v>
+      <c r="S6" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y6" s="3" t="n">
+      <c r="W6" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X6" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y6" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+      <c r="Z6" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1066,55 +1072,55 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>1.9</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="M7" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>4.8</v>
+      <c r="S7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+      <c r="X7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>2.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1136,70 +1142,70 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q8" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R8" s="3" t="n">
+      <c r="N8" s="9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>6</v>
+      <c r="S8" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="17" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.6</v>
+      <c r="W8" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1215,22 +1221,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>13.9</v>
+      <c r="G9" s="9" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1238,14 +1244,14 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>551.2</v>
+        <v>56.7</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1254,14 +1260,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="9" t="n">
         <v>101.5</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>185.3</v>
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1298,15 +1304,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="G10" s="9" t="n">
@@ -1318,36 +1324,36 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q10" s="10" t="n">
+      <c r="N10" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>117.7</v>
+        <v>16.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>6.7</v>
@@ -1355,16 +1361,18 @@
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="X10" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1390,26 +1398,26 @@
       <c r="F11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>18.6</v>
+      <c r="G11" s="9" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="3" t="n">
-        <v>26</v>
+      <c r="K11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1420,34 +1428,34 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="12" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="12" t="n">
-        <v>19.9</v>
+      <c r="S11" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>14.7</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z11" s="3" t="n">
+      <c r="Y11" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z11" s="9" t="n">
         <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1464,7 +1472,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.9</v>
@@ -1482,18 +1490,18 @@
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>11</v>
+      <c r="K12" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1505,20 +1513,20 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>20.4</v>
+      <c r="S12" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>14.8</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>21.3</v>
@@ -1552,58 +1560,58 @@
         <v>357.9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K13" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>185.4</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>13</v>
+      <c r="S13" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>19.6</v>
@@ -1637,13 +1645,13 @@
         <v>227</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>10.5</v>
@@ -1651,19 +1659,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="12" t="n">
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1673,30 +1681,30 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0.6</v>
+        <v>16.7</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="12" t="n">
+      <c r="W14" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X14" s="12" t="n">
+      <c r="X14" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1725,13 +1733,13 @@
         <v>26</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>50.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1740,19 +1748,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K15" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="17" t="n">
-        <v>77.40000000000001</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1760,20 +1768,20 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="12" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="S15" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="12" t="n">
-        <v>17.8</v>
+      <c r="U15" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>20.7</v>
@@ -1804,14 +1812,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>56.3</v>
+      <c r="E16" s="10" t="n">
+        <v>57</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>91.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>71.2</v>
@@ -1825,11 +1833,11 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>5.9</v>
+        <v>59.1</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>58.2</v>
@@ -1838,31 +1846,31 @@
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="10" t="n">
-        <v>1111</v>
-      </c>
-      <c r="R16" s="9" t="n">
+      <c r="Q16" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="R16" s="10" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>98.2</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>801.9</v>
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1905,10 +1913,10 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>29.4</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="10" t="n">
@@ -1917,29 +1925,29 @@
       <c r="M17" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q17" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q17" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>362</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>18.2</v>
+      <c r="S17" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>19.6</v>
@@ -1947,14 +1955,14 @@
       <c r="W17" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="12" t="n">
-        <v>16.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>872.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1978,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>25.9</v>
@@ -1979,21 +1987,21 @@
         <v>10.9</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="9" t="n">
@@ -2014,32 +2022,32 @@
       <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="R18" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="S18" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="12" t="n">
+      <c r="T18" s="9" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="9" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+      <c r="X18" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z18" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2066,8 +2074,8 @@
       <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>17.9</v>
+      <c r="G19" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2078,7 +2086,7 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
@@ -2099,17 +2107,17 @@
       <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="R19" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S19" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="9" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="12" t="n">
-        <v>7.2</v>
+      <c r="U19" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>21.2</v>
@@ -2157,26 +2165,26 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N20" s="12" t="n">
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2184,32 +2192,32 @@
       <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="R20" s="9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S20" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="T20" s="3" t="n">
+      <c r="T20" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="12" t="n">
-        <v>222.4</v>
+      <c r="U20" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>7.6</v>
+      <c r="W20" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Z20" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2230,13 +2238,13 @@
       <c r="D21" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2246,54 +2254,54 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P21" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="P21" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S21" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>1.6</v>
+      <c r="U21" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X21" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Y21" s="3" t="n">
+      <c r="W21" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Z21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2310,22 +2318,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>429</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2333,53 +2341,53 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>8</v>
+      <c r="K22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P22" s="3" t="n">
+      <c r="N22" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S22" s="3" t="n">
+      <c r="R22" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S22" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
+      <c r="T22" s="9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="U22" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+      <c r="X22" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z22" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2395,43 +2403,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
+        <v>2320.3</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>132.1</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>50.1</v>
+        <v>56.7</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+      <c r="G23" s="9" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>62.5</v>
+        <v>67</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>11.4</v>
@@ -2440,10 +2448,10 @@
         <v>128.9</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2485,10 +2493,10 @@
       <c r="D24" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G24" s="9" t="n">
@@ -2501,10 +2509,10 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>12.5</v>
@@ -2513,7 +2521,7 @@
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2527,29 +2535,29 @@
       <c r="R24" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>17.8</v>
+      <c r="S24" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>13.1</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>17.1</v>
+      </c>
+      <c r="X24" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2576,35 +2584,35 @@
       <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>10.9</v>
+      <c r="G25" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>24.7</v>
@@ -2650,7 +2658,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>24.4</v>
@@ -2667,29 +2675,29 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K26" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0.9</v>
+      <c r="N26" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>21</v>
@@ -2709,17 +2717,17 @@
       <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X26" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y26" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="Z26" s="9" t="n">
-        <v>8.199999999999999</v>
+      <c r="W26" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,16 +2746,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>24</v>
+      <c r="G27" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2756,25 +2764,25 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.4</v>
+      <c r="N27" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>17.6</v>
@@ -2794,17 +2802,17 @@
       <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>0.9</v>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2826,16 +2834,16 @@
         <v>27</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>15.9</v>
+      <c r="G28" s="9" t="n">
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2843,11 +2851,11 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>13.3</v>
@@ -2856,10 +2864,10 @@
         <v>15.3</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>98.7</v>
+        <v>99.3</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>22.9</v>
@@ -2879,17 +2887,17 @@
       <c r="V28" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y28" s="9" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Z28" s="9" t="n">
-        <v>1</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2913,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>28.8</v>
@@ -2917,7 +2925,7 @@
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2928,53 +2936,53 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>2.6</v>
+      <c r="N29" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>27</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>47.8</v>
+        <v>60.4</v>
       </c>
       <c r="U29" s="9" t="n">
-        <v>18.6</v>
+        <v>14.1</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>71.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2990,22 +2998,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>131.8</v>
+        <v>131.2</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>51.4</v>
+        <v>52.1</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="9" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3013,14 +3021,14 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v>56.7</v>
+        <v>57.2</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -3034,7 +3042,7 @@
       <c r="Q30" s="9" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="9" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3044,7 +3052,7 @@
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>99.5</v>
@@ -3052,14 +3060,14 @@
       <c r="W30" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>522</v>
-      </c>
-      <c r="Y30" s="9" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="Z30" s="9" t="n">
-        <v>506.8</v>
+      <c r="X30" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3075,7 +3083,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>26.2</v>
@@ -3100,34 +3108,34 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M31" s="10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="O31" s="9" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="P31" s="9" t="n">
+      <c r="O31" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="10" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" s="12" t="n">
-        <v>111.4</v>
+      <c r="R31" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>7.7</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>19.9</v>
@@ -3135,14 +3143,14 @@
       <c r="W31" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y31" s="9" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Z31" s="9" t="n">
-        <v>4.6</v>
+      <c r="X31" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>730.2</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3175,7 @@
         <v>10.2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>17.7</v>
@@ -3181,11 +3189,11 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>20.5</v>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>10.2</v>
@@ -3193,39 +3201,39 @@
       <c r="N32" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O32" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>26.46</v>
+      <c r="O32" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T32" s="9" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="V32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+      <c r="X32" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y32" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3256,61 +3264,61 @@
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q33" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>19.9</v>
+      <c r="S33" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>19.4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>14</v>
+      <c r="X33" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y33" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z33" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3326,7 +3334,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>23.3</v>
@@ -3340,62 +3348,62 @@
       <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>14.7</v>
+      <c r="H34" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O34" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O34" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="P34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="U34" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>28.7</v>
+      <c r="S34" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+      <c r="X34" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Z34" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3434,7 +3442,7 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
@@ -3444,43 +3452,43 @@
         <v>12.9</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V35" s="12" t="n">
+      <c r="S35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V35" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>8</v>
+      <c r="X35" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3502,70 +3510,70 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="9" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>8.6</v>
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T36" s="9" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V36" s="3" t="n">
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>11</v>
+      <c r="X36" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>7.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3581,37 +3589,37 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>62.6</v>
+      <c r="G37" s="9" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L37" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>63.7</v>
+      <c r="K37" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
@@ -3620,32 +3628,32 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="9" t="n">
-        <v>115.9</v>
+      <c r="Q37" s="10" t="n">
+        <v>115.5</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>88.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="9" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3664,7 +3672,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>25.7</v>
@@ -3684,11 +3692,13 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="J38" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9" t="n">
         <v>13</v>
       </c>
       <c r="M38" s="9" t="n">
@@ -3698,40 +3708,40 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T38" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="V38" s="10" t="n">
+      <c r="S38" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>6.9</v>
+      <c r="X38" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y38" s="9" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="Z38" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3750,7 +3760,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>11</v>
@@ -3762,59 +3772,61 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>12.1</v>
+      <c r="L39" s="9" t="n">
+        <v>12.7</v>
       </c>
       <c r="M39" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="12" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>9.4</v>
+      <c r="N39" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V39" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="17" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v>176</v>
+      <c r="S39" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="V39" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Y39" s="9" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="Z39" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3830,7 +3842,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>27.2</v>
@@ -3853,53 +3865,53 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>10.2</v>
+      <c r="N40" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" s="12" t="n">
+      <c r="R40" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S40" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="T40" s="3" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="U40" s="3" t="n">
+      <c r="T40" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U40" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="12" t="n">
+      <c r="V40" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y40" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>83</v>
+      <c r="X40" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="Z40" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3918,73 +3930,73 @@
         <v>451.2</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>28.94</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G41" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G41" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>4.9</v>
+        <v>11.2</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V41" s="3" t="n">
+      <c r="S41" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="V41" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="17" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+      <c r="W41" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Y41" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z41" s="9" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4005,61 +4017,61 @@
       <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="17" t="n">
-        <v>1.1</v>
+      <c r="E42" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="17" t="n">
-        <v>12.6</v>
+      <c r="G42" s="9" t="n">
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>11.7</v>
+      <c r="L42" s="9" t="n">
+        <v>11.9</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>0.8</v>
+        <v>13.4</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="V42" s="3" t="n">
+      <c r="R42" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T42" s="9" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="16" t="inlineStr"/>
+      <c r="W42" s="9" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4086,19 +4098,19 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
-      <c r="L43" s="16" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="16" t="inlineStr"/>
+      <c r="R43" s="20" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="16" t="inlineStr"/>
-      <c r="W43" s="16" t="inlineStr"/>
+      <c r="V43" s="9" t="inlineStr"/>
+      <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4125,19 +4137,19 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="16" t="inlineStr"/>
+      <c r="R44" s="20" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="16" t="inlineStr"/>
-      <c r="W44" s="16" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4155,49 +4167,49 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
+        <v>1911.2</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>110.2</v>
+        <v>109.7</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>10.8</v>
+      <c r="G45" s="3" t="n">
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="10" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
       <c r="M45" s="9" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>99.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>71</v>
@@ -4211,14 +4223,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="10" t="n">
-        <v>831.9</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>67.3</v>
+      <c r="V45" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>51</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4245,7 +4257,7 @@
       <c r="D46" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="F46" s="9" t="n">
@@ -4261,13 +4273,13 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="10" t="n">
-        <v>111.7</v>
+        <v>52.1</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="M46" s="9" t="n">
         <v>10.7</v>
@@ -4276,10 +4288,10 @@
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>24.7</v>
@@ -4287,29 +4299,29 @@
       <c r="R46" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V46" s="10" t="n">
+      <c r="S46" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V46" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>265.7</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+      <c r="X46" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y46" s="9" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Z46" s="9" t="n">
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
